--- a/results/MC_Dist=Exp_n=500_LT=0.1_C=0.4_B=100.xlsx
+++ b/results/MC_Dist=Exp_n=500_LT=0.1_C=0.4_B=100.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -123,13 +123,16 @@
     <t xml:space="preserve">Gamma</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5,1</t>
+    <t xml:space="preserve">1,0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x1.mean</t>
   </si>
   <si>
     <t xml:space="preserve">x1.sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x2.mean</t>
@@ -545,22 +548,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.07446922291499</v>
+        <v>-1.0256645622857</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0744692229149897</v>
+        <v>-0.0256645622857008</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0234432761744431</v>
+        <v>0.0208158566176723</v>
       </c>
       <c r="E2" t="n">
-        <v>0.134455922006082</v>
+        <v>0.142691256944636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="G2" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="3">
@@ -568,19 +571,19 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.01687289754723</v>
+        <v>-1.00451468486348</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0168728975472257</v>
+        <v>-0.00451468486348139</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0179174762878949</v>
+        <v>0.0126925327216622</v>
       </c>
       <c r="E3" t="n">
-        <v>0.133457448355161</v>
+        <v>0.113137756124356</v>
       </c>
       <c r="F3" t="n">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="G3" t="n">
         <v>0.98</v>
@@ -591,22 +594,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1.55956825542657</v>
+        <v>1.05296920092493</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0595682554265733</v>
+        <v>0.0529692009249267</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0327693573070406</v>
+        <v>0.0248749439666378</v>
       </c>
       <c r="E4" t="n">
-        <v>0.171802624162632</v>
+        <v>0.149305488881399</v>
       </c>
       <c r="F4" t="n">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="G4" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="5">
@@ -614,19 +617,19 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1.24865575380755</v>
+        <v>0.964605039389349</v>
       </c>
       <c r="C5" t="n">
-        <v>0.248655753807553</v>
+        <v>0.164605039389349</v>
       </c>
       <c r="D5" t="n">
-        <v>0.139923281924821</v>
+        <v>0.0940485584982414</v>
       </c>
       <c r="E5" t="n">
-        <v>0.280860147129627</v>
+        <v>0.260057762631538</v>
       </c>
       <c r="F5" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="G5" t="n">
         <v>0.96</v>
@@ -637,19 +640,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>1.99730944972852</v>
+        <v>1.98600331335473</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.00269055027148335</v>
+        <v>-0.013996686645267</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00340806407544716</v>
+        <v>0.00455974945958543</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0586103811837875</v>
+        <v>0.0663921790341958</v>
       </c>
       <c r="F6" t="n">
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
       <c r="G6" t="n">
         <v>0.99</v>
@@ -783,20 +786,20 @@
         <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -815,2325 +818,2325 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1.17749645656415</v>
+        <v>-0.833803713548806</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.21483619013607</v>
+        <v>-1.00074746063879</v>
       </c>
       <c r="C2" t="n">
-        <v>1.66591307190809</v>
+        <v>1.02623330617161</v>
       </c>
       <c r="D2" t="n">
-        <v>1.49431038110615</v>
+        <v>0.677878369760333</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.932824313376969</v>
+        <v>-1.14285520697036</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.23963835880118</v>
+        <v>-1.62278348202251</v>
       </c>
       <c r="G2" t="n">
-        <v>1.99222456781517</v>
+        <v>2.01984211984628</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1.0849881999529</v>
+        <v>-0.942279195792737</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.03860496474627</v>
+        <v>-1.1486772078901</v>
       </c>
       <c r="C3" t="n">
-        <v>1.72378779960368</v>
+        <v>1.24398219452654</v>
       </c>
       <c r="D3" t="n">
-        <v>1.31735391832149</v>
+        <v>0.734113054966731</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.741365099456116</v>
+        <v>-1.19414479534843</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.39499249994243</v>
+        <v>-1.60856553184349</v>
       </c>
       <c r="G3" t="n">
-        <v>2.01107328641036</v>
+        <v>1.99574354676789</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-1.26845582168189</v>
+        <v>-0.867138728654353</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.854177810792699</v>
+        <v>-0.845361594576311</v>
       </c>
       <c r="C4" t="n">
-        <v>1.31165743467523</v>
+        <v>0.799958424528323</v>
       </c>
       <c r="D4" t="n">
-        <v>1.62042144940432</v>
+        <v>0.662197561296577</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.852306038074372</v>
+        <v>-1.27803894240308</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.29587837875645</v>
+        <v>-1.65566804454985</v>
       </c>
       <c r="G4" t="n">
-        <v>1.93669055419943</v>
+        <v>2.05423482416332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-1.22249506466012</v>
+        <v>-1.07475280409181</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.09470692861</v>
+        <v>-0.937445148017772</v>
       </c>
       <c r="C5" t="n">
-        <v>1.77153861736951</v>
+        <v>1.0529841047507</v>
       </c>
       <c r="D5" t="n">
-        <v>1.37499894640496</v>
+        <v>1.15727411589367</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.43679676357346</v>
+        <v>-0.988866529052391</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.12898512423837</v>
+        <v>-1.53218272849896</v>
       </c>
       <c r="G5" t="n">
-        <v>2.07381400461678</v>
+        <v>1.93729783731802</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.07134779166783</v>
+        <v>-0.85466346212961</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.962701464572483</v>
+        <v>-1.12799653540548</v>
       </c>
       <c r="C6" t="n">
-        <v>1.42320784666115</v>
+        <v>1.2469870895668</v>
       </c>
       <c r="D6" t="n">
-        <v>1.57347256066403</v>
+        <v>0.660912733565646</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.13225135589423</v>
+        <v>-1.06180745819741</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.45357072772661</v>
+        <v>-1.6519148995127</v>
       </c>
       <c r="G6" t="n">
-        <v>2.01923737914545</v>
+        <v>1.98157678893521</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.90824292177452</v>
+        <v>-1.17127123466434</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.887744068841344</v>
+        <v>-1.02672923709431</v>
       </c>
       <c r="C7" t="n">
-        <v>1.47356534717952</v>
+        <v>1.09587116519268</v>
       </c>
       <c r="D7" t="n">
-        <v>1.09237356685004</v>
+        <v>1.29711961563191</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.902209286730979</v>
+        <v>-1.12291684606384</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.54362896535607</v>
+        <v>-1.28446280008095</v>
       </c>
       <c r="G7" t="n">
-        <v>2.03271812644471</v>
+        <v>2.04413602318323</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-1.02348491942872</v>
+        <v>-1.1059443283985</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.851330996255406</v>
+        <v>-0.804256890736515</v>
       </c>
       <c r="C8" t="n">
-        <v>1.34322546657189</v>
+        <v>0.84526983688063</v>
       </c>
       <c r="D8" t="n">
-        <v>1.21375565680707</v>
+        <v>1.15027602487548</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.765358788790927</v>
+        <v>-0.972869479611828</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.36898546964075</v>
+        <v>-1.25408775123706</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0142257961489</v>
+        <v>2.05342449997868</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-1.02349484837826</v>
+        <v>-1.07531248991217</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.16882622942926</v>
+        <v>-0.873864283329724</v>
       </c>
       <c r="C9" t="n">
-        <v>1.55085775715726</v>
+        <v>0.97275961817792</v>
       </c>
       <c r="D9" t="n">
-        <v>1.27259627636054</v>
+        <v>0.958426242240794</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.857718789766924</v>
+        <v>-1.09958112096884</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.42366023052608</v>
+        <v>-1.2922458964295</v>
       </c>
       <c r="G9" t="n">
-        <v>2.01300997283136</v>
+        <v>1.88551158420695</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-1.38390998328851</v>
+        <v>-1.14059085558366</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.01075648306849</v>
+        <v>-0.967884968512529</v>
       </c>
       <c r="C10" t="n">
-        <v>1.46653709514711</v>
+        <v>1.01984042670334</v>
       </c>
       <c r="D10" t="n">
-        <v>1.89290924364862</v>
+        <v>1.22633847037923</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.603706066689965</v>
+        <v>-0.667536546967162</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.17867937472144</v>
+        <v>-1.18567166144755</v>
       </c>
       <c r="G10" t="n">
-        <v>1.87769535904211</v>
+        <v>2.08795298367231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-1.23898496778875</v>
+        <v>-1.02565421078221</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.00854454726049</v>
+        <v>-0.738480275639042</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5289234300069</v>
+        <v>0.762556301771235</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6872700681339</v>
+        <v>0.841552364210384</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.77245718574073</v>
+        <v>-0.929935831878307</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.21829630872221</v>
+        <v>-1.33793130127311</v>
       </c>
       <c r="G11" t="n">
-        <v>1.94461523568436</v>
+        <v>1.95704108001292</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-1.05493147314875</v>
+        <v>-0.951965422289289</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.904602414202524</v>
+        <v>-1.03359358228416</v>
       </c>
       <c r="C12" t="n">
-        <v>1.44929884921394</v>
+        <v>1.07093698261556</v>
       </c>
       <c r="D12" t="n">
-        <v>1.28236140684073</v>
+        <v>0.883625104716274</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2265228548356</v>
+        <v>-1.04434242554387</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2669846235575</v>
+        <v>-1.520969062743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.00554153927185</v>
+        <v>1.973665105246</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-1.04642908495587</v>
+        <v>-1.14656265176293</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.00402902894455</v>
+        <v>-0.950471753661613</v>
       </c>
       <c r="C13" t="n">
-        <v>1.54033817368087</v>
+        <v>0.961229567761515</v>
       </c>
       <c r="D13" t="n">
-        <v>1.12172649268485</v>
+        <v>1.22974844870924</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.717003762840754</v>
+        <v>-0.622549238132173</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.29226569386524</v>
+        <v>-1.27634954370086</v>
       </c>
       <c r="G13" t="n">
-        <v>2.01765475817536</v>
+        <v>1.99981804343946</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.870779074610539</v>
+        <v>-0.923718169547807</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.927088328378052</v>
+        <v>-0.996419107930323</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3788622575563</v>
+        <v>1.11487630780086</v>
       </c>
       <c r="D14" t="n">
-        <v>0.814658457904039</v>
+        <v>0.957746057539694</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.02015134937523</v>
+        <v>-1.1389522472847</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.50580147957533</v>
+        <v>-1.57673335276201</v>
       </c>
       <c r="G14" t="n">
-        <v>2.07712662354565</v>
+        <v>2.05183683888249</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-1.21402040825079</v>
+        <v>-1.1029655615914</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.924079506979486</v>
+        <v>-0.916333913053663</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2610632174604</v>
+        <v>1.18023795584429</v>
       </c>
       <c r="D15" t="n">
-        <v>1.39735936032065</v>
+        <v>0.975765575390474</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.480770481439567</v>
+        <v>-0.748185346583156</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.19801095992865</v>
+        <v>-1.11997506185748</v>
       </c>
       <c r="G15" t="n">
-        <v>1.94989840406555</v>
+        <v>1.98771035797153</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.932209822132779</v>
+        <v>-0.946806960755915</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.07595345328437</v>
+        <v>-1.17791266410826</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6684665701787</v>
+        <v>1.21191071065532</v>
       </c>
       <c r="D16" t="n">
-        <v>1.05524436737461</v>
+        <v>1.04184332097189</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.993072104133929</v>
+        <v>-0.978556167916569</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.47291939126884</v>
+        <v>-1.6283169908018</v>
       </c>
       <c r="G16" t="n">
-        <v>1.99734196733962</v>
+        <v>2.03019898237361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-1.13144470908016</v>
+        <v>-0.858220232745728</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.990212565087288</v>
+        <v>-1.01716865425765</v>
       </c>
       <c r="C17" t="n">
-        <v>1.62597980730178</v>
+        <v>0.978934937031751</v>
       </c>
       <c r="D17" t="n">
-        <v>1.32388844986386</v>
+        <v>0.988246243086687</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.905890462805972</v>
+        <v>-1.41577833341206</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.31496932625629</v>
+        <v>-1.7993448636009</v>
       </c>
       <c r="G17" t="n">
-        <v>1.99390061639777</v>
+        <v>1.99575718391935</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.920489198697652</v>
+        <v>-0.752748420011062</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.976686728461694</v>
+        <v>-0.863623608263511</v>
       </c>
       <c r="C18" t="n">
-        <v>1.49436346500661</v>
+        <v>0.766092713924949</v>
       </c>
       <c r="D18" t="n">
-        <v>0.946295543812797</v>
+        <v>0.420918229878881</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1299106518798</v>
+        <v>-1.12427710546496</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.62927418900642</v>
+        <v>-1.6418965517349</v>
       </c>
       <c r="G18" t="n">
-        <v>1.93608228888321</v>
+        <v>1.93516230001418</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-1.0869178276029</v>
+        <v>-1.00188478465888</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.927862667558452</v>
+        <v>-1.10814702246458</v>
       </c>
       <c r="C19" t="n">
-        <v>1.40967756246606</v>
+        <v>1.19575491172268</v>
       </c>
       <c r="D19" t="n">
-        <v>1.12579523842487</v>
+        <v>0.957986932622887</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.58833236264116</v>
+        <v>-1.23314027154709</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.29004862954475</v>
+        <v>-2.34738994373902</v>
       </c>
       <c r="G19" t="n">
-        <v>2.00912927976672</v>
+        <v>1.9346440843693</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-1.02793513581358</v>
+        <v>-1.02266386491678</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.18522076926656</v>
+        <v>-0.895146598484225</v>
       </c>
       <c r="C20" t="n">
-        <v>1.70494339862795</v>
+        <v>0.906113947078937</v>
       </c>
       <c r="D20" t="n">
-        <v>1.14077663344271</v>
+        <v>0.967428351518498</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.07734823803709</v>
+        <v>-0.966143007179593</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.56271060736282</v>
+        <v>-1.29393097389832</v>
       </c>
       <c r="G20" t="n">
-        <v>1.93189518135285</v>
+        <v>2.01138470008029</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.929318895094651</v>
+        <v>-1.01712769580727</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.06978829406687</v>
+        <v>-0.834930703863138</v>
       </c>
       <c r="C21" t="n">
-        <v>1.47614239423657</v>
+        <v>0.640000905037119</v>
       </c>
       <c r="D21" t="n">
-        <v>1.04361359500486</v>
+        <v>0.995270824466696</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.950128150259049</v>
+        <v>-0.985109055990135</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.52034820048584</v>
+        <v>-1.32951254988952</v>
       </c>
       <c r="G21" t="n">
-        <v>1.93464788729993</v>
+        <v>2.0156044597932</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-1.12790789368016</v>
+        <v>-0.779581517148687</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.19511275260369</v>
+        <v>-1.30984597978774</v>
       </c>
       <c r="C22" t="n">
-        <v>1.72308089931221</v>
+        <v>1.31990541220378</v>
       </c>
       <c r="D22" t="n">
-        <v>1.20943194657071</v>
+        <v>0.499238913294233</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.840098010945854</v>
+        <v>-1.31548093808942</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.31532688833592</v>
+        <v>-2.46341299185958</v>
       </c>
       <c r="G22" t="n">
-        <v>1.94960291291062</v>
+        <v>1.95962066282247</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-1.22462217838064</v>
+        <v>-1.05216856712065</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.882961285494148</v>
+        <v>-1.12225894030508</v>
       </c>
       <c r="C23" t="n">
-        <v>1.37229616697146</v>
+        <v>1.15240753968089</v>
       </c>
       <c r="D23" t="n">
-        <v>1.57227042398872</v>
+        <v>1.26612017467125</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.00354816357822</v>
+        <v>-1.08627378835453</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.149897790007</v>
+        <v>-1.52984918592034</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95995509601518</v>
+        <v>1.95119962604498</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-1.05218331020552</v>
+        <v>-1.33591761353877</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.982051198660855</v>
+        <v>-1.07396175734237</v>
       </c>
       <c r="C24" t="n">
-        <v>1.64994918947925</v>
+        <v>1.16967527585065</v>
       </c>
       <c r="D24" t="n">
-        <v>1.20717528719796</v>
+        <v>1.55174731702825</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.15291005329098</v>
+        <v>-0.680703555761296</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.00928055756731</v>
+        <v>-1.07401468836453</v>
       </c>
       <c r="G24" t="n">
-        <v>2.02302966126588</v>
+        <v>1.9641101087583</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-0.983003145299498</v>
+        <v>-1.00307081141081</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.951390620296743</v>
+        <v>-0.988803730909483</v>
       </c>
       <c r="C25" t="n">
-        <v>1.66614963611157</v>
+        <v>1.17207544717289</v>
       </c>
       <c r="D25" t="n">
-        <v>1.21281460803339</v>
+        <v>0.811699597265929</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.13131200831098</v>
+        <v>-0.969706010023816</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.44157657741255</v>
+        <v>-1.37245500806196</v>
       </c>
       <c r="G25" t="n">
-        <v>2.13268716459516</v>
+        <v>2.03329478779377</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-1.04065317261485</v>
+        <v>-1.25661850045712</v>
       </c>
       <c r="B26" t="n">
-        <v>-1.10831015891364</v>
+        <v>-1.02400961041203</v>
       </c>
       <c r="C26" t="n">
-        <v>1.73331992912889</v>
+        <v>1.08820038423714</v>
       </c>
       <c r="D26" t="n">
-        <v>1.09031987309905</v>
+        <v>1.49601632493399</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.859019938075249</v>
+        <v>-0.885034461018812</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.38460233059185</v>
+        <v>-1.22781193752465</v>
       </c>
       <c r="G26" t="n">
-        <v>1.99344587703255</v>
+        <v>1.98102056220436</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.98478503909809</v>
+        <v>-1.01254421826839</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.780030409526944</v>
+        <v>-0.959215891217944</v>
       </c>
       <c r="C27" t="n">
-        <v>1.29458294491289</v>
+        <v>1.15649821359706</v>
       </c>
       <c r="D27" t="n">
-        <v>1.22878233953534</v>
+        <v>0.789356967354101</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.06887153061853</v>
+        <v>-0.817969000240377</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.49006624631947</v>
+        <v>-1.28814972879616</v>
       </c>
       <c r="G27" t="n">
-        <v>1.95528401312111</v>
+        <v>2.00364562959756</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-0.886312431041206</v>
+        <v>-1.00840206683691</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.943224011666786</v>
+        <v>-0.856176269849397</v>
       </c>
       <c r="C28" t="n">
-        <v>1.45790772894576</v>
+        <v>0.797383698751482</v>
       </c>
       <c r="D28" t="n">
-        <v>0.797413090348092</v>
+        <v>0.861407531398757</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.2209140946791</v>
+        <v>-0.836449561879925</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.50437078676789</v>
+        <v>-1.29721384102645</v>
       </c>
       <c r="G28" t="n">
-        <v>2.09590736192996</v>
+        <v>2.02737739783342</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-1.02901861049767</v>
+        <v>-0.848816726610131</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.942942996560403</v>
+        <v>-0.863933130287864</v>
       </c>
       <c r="C29" t="n">
-        <v>1.52609684671956</v>
+        <v>0.869043725971536</v>
       </c>
       <c r="D29" t="n">
-        <v>1.10654034969958</v>
+        <v>0.808830642319378</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.00954806421966</v>
+        <v>-1.18318896104885</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.37709819703903</v>
+        <v>-1.73206601687491</v>
       </c>
       <c r="G29" t="n">
-        <v>1.99711061150227</v>
+        <v>2.00961506260232</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-0.925358585490897</v>
+        <v>-1.15083417449839</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.792893515498041</v>
+        <v>-1.19741793520628</v>
       </c>
       <c r="C30" t="n">
-        <v>1.41647410973304</v>
+        <v>1.23149966204781</v>
       </c>
       <c r="D30" t="n">
-        <v>0.856834962622992</v>
+        <v>1.26580534950917</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.892696289043694</v>
+        <v>-0.940016588726486</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.44582316975631</v>
+        <v>-1.23626310625452</v>
       </c>
       <c r="G30" t="n">
-        <v>2.1631288453878</v>
+        <v>1.87268241683239</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-1.1338588316281</v>
+        <v>-1.12558143768851</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.940156230293604</v>
+        <v>-0.946289971868188</v>
       </c>
       <c r="C31" t="n">
-        <v>1.38556660533679</v>
+        <v>0.91217492559642</v>
       </c>
       <c r="D31" t="n">
-        <v>1.14804496777281</v>
+        <v>1.33302632707318</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.931937988477137</v>
+        <v>-1.04110095361934</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.11690014116983</v>
+        <v>-1.51143134769237</v>
       </c>
       <c r="G31" t="n">
-        <v>1.99565808000009</v>
+        <v>1.91535541164363</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-0.990231417409495</v>
+        <v>-0.985351572107634</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.960066763247697</v>
+        <v>-1.03520100539354</v>
       </c>
       <c r="C32" t="n">
-        <v>1.52420332573418</v>
+        <v>1.02045399544966</v>
       </c>
       <c r="D32" t="n">
-        <v>1.03286596555481</v>
+        <v>0.929798080277724</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.640722879133989</v>
+        <v>-1.1781821901963</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.25463241500069</v>
+        <v>-1.44773930971158</v>
       </c>
       <c r="G32" t="n">
-        <v>2.02600707234408</v>
+        <v>1.91786209328124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-1.08452952211761</v>
+        <v>-1.02904294369392</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.994677188099952</v>
+        <v>-1.13214539894257</v>
       </c>
       <c r="C33" t="n">
-        <v>1.56706195741938</v>
+        <v>1.1374395884987</v>
       </c>
       <c r="D33" t="n">
-        <v>0.855797948036667</v>
+        <v>1.09441891881087</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.930151226942924</v>
+        <v>-0.92549970326886</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.67498647640077</v>
+        <v>-1.51855427050377</v>
       </c>
       <c r="G33" t="n">
-        <v>2.02836198141023</v>
+        <v>1.98975282358398</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-1.04380166137552</v>
+        <v>-0.834187940332377</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.03669425591179</v>
+        <v>-0.993052864322707</v>
       </c>
       <c r="C34" t="n">
-        <v>1.53930724160344</v>
+        <v>1.23111075173374</v>
       </c>
       <c r="D34" t="n">
-        <v>0.885875977542231</v>
+        <v>0.749212510615983</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.72594900899712</v>
+        <v>-1.63875970151694</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.21059615248645</v>
+        <v>-1.81300465211784</v>
       </c>
       <c r="G34" t="n">
-        <v>1.98290931574283</v>
+        <v>1.98742949060748</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-1.13627955071209</v>
+        <v>-0.847687527447475</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.876132546313798</v>
+        <v>-1.0856745314727</v>
       </c>
       <c r="C35" t="n">
-        <v>1.33486164948006</v>
+        <v>1.14267834056352</v>
       </c>
       <c r="D35" t="n">
-        <v>1.39003085155504</v>
+        <v>0.681306556483454</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.533173544592669</v>
+        <v>-1.19905707904992</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.30363523827338</v>
+        <v>-1.72206083333237</v>
       </c>
       <c r="G35" t="n">
-        <v>2.02298541687867</v>
+        <v>2.00843824432926</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-1.19283381957069</v>
+        <v>-1.0344262269718</v>
       </c>
       <c r="B36" t="n">
-        <v>-1.08300698558936</v>
+        <v>-1.23149323842059</v>
       </c>
       <c r="C36" t="n">
-        <v>1.64477328866665</v>
+        <v>1.25165771228895</v>
       </c>
       <c r="D36" t="n">
-        <v>1.58968559133303</v>
+        <v>0.921357298779419</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.10078661480563</v>
+        <v>-1.05714832393321</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.29918470673321</v>
+        <v>-1.29507170005263</v>
       </c>
       <c r="G36" t="n">
-        <v>2.00492844720829</v>
+        <v>1.83960756986344</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-1.13990198128943</v>
+        <v>-1.17959762170309</v>
       </c>
       <c r="B37" t="n">
-        <v>-1.20464667657629</v>
+        <v>-1.03614497273832</v>
       </c>
       <c r="C37" t="n">
-        <v>1.69184738404676</v>
+        <v>1.00588281738203</v>
       </c>
       <c r="D37" t="n">
-        <v>1.42150844365097</v>
+        <v>1.18578567335185</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.18619859322014</v>
+        <v>-0.927580615214956</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.16915369871593</v>
+        <v>-1.9729798760448</v>
       </c>
       <c r="G37" t="n">
-        <v>1.9448152062833</v>
+        <v>2.02208156419164</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-1.02869520763689</v>
+        <v>-0.911928349625171</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.947000129298346</v>
+        <v>-1.08364008035375</v>
       </c>
       <c r="C38" t="n">
-        <v>1.51735472168969</v>
+        <v>1.25488425918177</v>
       </c>
       <c r="D38" t="n">
-        <v>1.0998653465797</v>
+        <v>0.69629587246756</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.951636632086879</v>
+        <v>-0.958087685018341</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.31636603728352</v>
+        <v>-1.53459801385891</v>
       </c>
       <c r="G38" t="n">
-        <v>2.05060455702607</v>
+        <v>1.86983381453121</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-1.26217270239205</v>
+        <v>-1.1157393552778</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.760937737400598</v>
+        <v>-0.998396597126735</v>
       </c>
       <c r="C39" t="n">
-        <v>1.38680957602293</v>
+        <v>0.958517408219228</v>
       </c>
       <c r="D39" t="n">
-        <v>1.59943941417088</v>
+        <v>1.10705085621691</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.715659473214758</v>
+        <v>-0.842624907719628</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.20738845419651</v>
+        <v>-1.33772173465199</v>
       </c>
       <c r="G39" t="n">
-        <v>2.06015944134191</v>
+        <v>1.95499326240892</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-1.06564517675808</v>
+        <v>-1.22154769409824</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.789426933529383</v>
+        <v>-1.30428773241243</v>
       </c>
       <c r="C40" t="n">
-        <v>1.37265130721109</v>
+        <v>1.44950166741699</v>
       </c>
       <c r="D40" t="n">
-        <v>1.16142493274629</v>
+        <v>1.21792961898235</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.8447797106584</v>
+        <v>-0.909203776537474</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.26627473352767</v>
+        <v>-2.1264645807982</v>
       </c>
       <c r="G40" t="n">
-        <v>2.05706656156118</v>
+        <v>1.93670900523237</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-1.03308883623784</v>
+        <v>-1.16391463570198</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.915352257986126</v>
+        <v>-0.832857311021127</v>
       </c>
       <c r="C41" t="n">
-        <v>1.19477328446394</v>
+        <v>0.873026215211429</v>
       </c>
       <c r="D41" t="n">
-        <v>1.16298587063318</v>
+        <v>1.15785899177434</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.899015658521939</v>
+        <v>-0.839687793596992</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.44014009681446</v>
+        <v>-1.28917332008363</v>
       </c>
       <c r="G41" t="n">
-        <v>1.96524873233108</v>
+        <v>2.07721544431009</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-1.05110888963806</v>
+        <v>-1.09752802155877</v>
       </c>
       <c r="B42" t="n">
-        <v>-1.13805427755383</v>
+        <v>-0.957531228118824</v>
       </c>
       <c r="C42" t="n">
-        <v>1.69802442246096</v>
+        <v>1.15569249405711</v>
       </c>
       <c r="D42" t="n">
-        <v>1.32156137288412</v>
+        <v>0.927358551541719</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.21642024097919</v>
+        <v>-0.922609849058832</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.02604492921278</v>
+        <v>-1.25015051149292</v>
       </c>
       <c r="G42" t="n">
-        <v>2.03057365785337</v>
+        <v>2.01204007046356</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-0.957244357723021</v>
+        <v>-1.02702619453383</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.96063652259114</v>
+        <v>-0.979299394077368</v>
       </c>
       <c r="C43" t="n">
-        <v>1.46237571323374</v>
+        <v>1.07278415102794</v>
       </c>
       <c r="D43" t="n">
-        <v>1.07101210833668</v>
+        <v>0.997291242566405</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.18104727150595</v>
+        <v>-0.928005814836644</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.58051428494541</v>
+        <v>-1.46628164549019</v>
       </c>
       <c r="G43" t="n">
-        <v>2.09813203340416</v>
+        <v>2.05732315914734</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-0.829503583387922</v>
+        <v>-0.932018402292726</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.991939752180633</v>
+        <v>-0.937973412866254</v>
       </c>
       <c r="C44" t="n">
-        <v>1.53514890021079</v>
+        <v>0.912107590174219</v>
       </c>
       <c r="D44" t="n">
-        <v>0.915380706904287</v>
+        <v>0.507373906775696</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.29294893199681</v>
+        <v>-1.00021483331537</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.67892392306675</v>
+        <v>-1.41667525218081</v>
       </c>
       <c r="G44" t="n">
-        <v>1.99168686136152</v>
+        <v>1.91500379743865</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-0.950039191753613</v>
+        <v>-0.953649034267186</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.907331512420363</v>
+        <v>-1.03098694536009</v>
       </c>
       <c r="C45" t="n">
-        <v>1.32598108142434</v>
+        <v>1.06444538433844</v>
       </c>
       <c r="D45" t="n">
-        <v>1.05079370784886</v>
+        <v>0.971871486808994</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.01840395056135</v>
+        <v>-1.26186354983216</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.42184514597131</v>
+        <v>-1.53853685034778</v>
       </c>
       <c r="G45" t="n">
-        <v>2.13049431100188</v>
+        <v>1.93836819701991</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-1.07123395690939</v>
+        <v>-0.74018631757495</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.989430260928259</v>
+        <v>-0.894852932906173</v>
       </c>
       <c r="C46" t="n">
-        <v>1.45058594424813</v>
+        <v>0.943180761814125</v>
       </c>
       <c r="D46" t="n">
-        <v>1.33015303715402</v>
+        <v>0.479173087396058</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.998774266665823</v>
+        <v>-1.09927251227051</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.39121530229003</v>
+        <v>-1.67810914663928</v>
       </c>
       <c r="G46" t="n">
-        <v>1.93944336459773</v>
+        <v>2.11276926970587</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-0.971823121519948</v>
+        <v>-1.06992628592072</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.84427902766656</v>
+        <v>-0.91292252232414</v>
       </c>
       <c r="C47" t="n">
-        <v>1.47233706371156</v>
+        <v>0.909658984148091</v>
       </c>
       <c r="D47" t="n">
-        <v>1.11277783181707</v>
+        <v>1.07692839185027</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.00167976810996</v>
+        <v>-1.1477203205073</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.47835013320032</v>
+        <v>-1.4219641497641</v>
       </c>
       <c r="G47" t="n">
-        <v>2.01686326556012</v>
+        <v>1.9933992527527</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-1.01104050683237</v>
+        <v>-1.08072170921527</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.993957816998646</v>
+        <v>-1.07462162570899</v>
       </c>
       <c r="C48" t="n">
-        <v>1.49726844452772</v>
+        <v>1.14961703661039</v>
       </c>
       <c r="D48" t="n">
-        <v>1.21486129520801</v>
+        <v>0.934962150958234</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.892275433955449</v>
+        <v>-0.97113101726744</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.48597077899806</v>
+        <v>-1.37749425273099</v>
       </c>
       <c r="G48" t="n">
-        <v>2.01645257568096</v>
+        <v>1.91574809869497</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-1.18950451114073</v>
+        <v>-0.998469333531801</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.987997148964073</v>
+        <v>-0.938112803711153</v>
       </c>
       <c r="C49" t="n">
-        <v>1.51090185259999</v>
+        <v>0.994854041814905</v>
       </c>
       <c r="D49" t="n">
-        <v>1.17305600953001</v>
+        <v>0.942422558451613</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.880508454138186</v>
+        <v>-1.03126785081391</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.85445057893815</v>
+        <v>-1.46633547661001</v>
       </c>
       <c r="G49" t="n">
-        <v>1.98139277946962</v>
+        <v>1.98840841997627</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-1.15439984154944</v>
+        <v>-1.11202298727997</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.15465402599625</v>
+        <v>-1.04712192522787</v>
       </c>
       <c r="C50" t="n">
-        <v>1.57627601052176</v>
+        <v>1.13129771225076</v>
       </c>
       <c r="D50" t="n">
-        <v>1.54725705114799</v>
+        <v>1.06894920629493</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.3347288420917</v>
+        <v>-0.883991897257329</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.38672746639776</v>
+        <v>-1.34138287166674</v>
       </c>
       <c r="G50" t="n">
-        <v>1.89309498189902</v>
+        <v>1.92020650750459</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-1.00155328091704</v>
+        <v>-1.14943023278438</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.781768274094725</v>
+        <v>-1.02841395126123</v>
       </c>
       <c r="C51" t="n">
-        <v>1.38543880767207</v>
+        <v>1.04879290084546</v>
       </c>
       <c r="D51" t="n">
-        <v>1.1739027024618</v>
+        <v>1.04702218016599</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.06361146717104</v>
+        <v>-0.610375376318217</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.47993832813283</v>
+        <v>-1.18293787607815</v>
       </c>
       <c r="G51" t="n">
-        <v>1.8686659528794</v>
+        <v>2.08167820239945</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-0.821180488085136</v>
+        <v>-0.845833807944094</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.963924297729913</v>
+        <v>-1.04131328660971</v>
       </c>
       <c r="C52" t="n">
-        <v>1.45340429497441</v>
+        <v>1.17271799433713</v>
       </c>
       <c r="D52" t="n">
-        <v>0.850380491112259</v>
+        <v>0.713721019233564</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.22805920794432</v>
+        <v>-1.06887490982145</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.70819067951023</v>
+        <v>-1.63420004089671</v>
       </c>
       <c r="G52" t="n">
-        <v>1.99190166517827</v>
+        <v>1.89805593310503</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-1.28190066421374</v>
+        <v>-0.962124147303446</v>
       </c>
       <c r="B53" t="n">
-        <v>-1.06473875983922</v>
+        <v>-1.0437618651665</v>
       </c>
       <c r="C53" t="n">
-        <v>1.76881431579446</v>
+        <v>1.13951271730912</v>
       </c>
       <c r="D53" t="n">
-        <v>1.53470106726072</v>
+        <v>1.21184248816025</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.805005724260888</v>
+        <v>-1.30324756177512</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.02061995512825</v>
+        <v>-1.73091090891579</v>
       </c>
       <c r="G53" t="n">
-        <v>2.05585563486256</v>
+        <v>1.96770774783482</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-0.996032933816493</v>
+        <v>-1.14459634855621</v>
       </c>
       <c r="B54" t="n">
-        <v>-1.00195076564486</v>
+        <v>-1.18691984846787</v>
       </c>
       <c r="C54" t="n">
-        <v>1.48763524472776</v>
+        <v>1.13239344103393</v>
       </c>
       <c r="D54" t="n">
-        <v>1.30384295269637</v>
+        <v>0.988175900487569</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.96787275295262</v>
+        <v>-0.957518516195639</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.5219786327866</v>
+        <v>-1.93164650110054</v>
       </c>
       <c r="G54" t="n">
-        <v>2.03461295750525</v>
+        <v>1.88393210711881</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-1.07667146775278</v>
+        <v>-1.18698935868099</v>
       </c>
       <c r="B55" t="n">
-        <v>-1.10462519281196</v>
+        <v>-1.21161097777559</v>
       </c>
       <c r="C55" t="n">
-        <v>1.74095145604164</v>
+        <v>1.29430252505906</v>
       </c>
       <c r="D55" t="n">
-        <v>1.16893543289364</v>
+        <v>0.924882069570059</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.07742265367561</v>
+        <v>-0.920503283994433</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.13636290161687</v>
+        <v>-2.02818144110538</v>
       </c>
       <c r="G55" t="n">
-        <v>1.99293116753983</v>
+        <v>1.93929555515506</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-1.01741741356254</v>
+        <v>-1.18387676646648</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.912305815733541</v>
+        <v>-1.01869899220886</v>
       </c>
       <c r="C56" t="n">
-        <v>1.52009413304545</v>
+        <v>1.12909103058071</v>
       </c>
       <c r="D56" t="n">
-        <v>1.35692469400397</v>
+        <v>1.34010576332429</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.05493012262437</v>
+        <v>-0.971976357783735</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.43487879951093</v>
+        <v>-2.014903199076</v>
       </c>
       <c r="G56" t="n">
-        <v>2.00916737730472</v>
+        <v>1.9879039487327</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-0.803590532723046</v>
+        <v>-1.14867233623371</v>
       </c>
       <c r="B57" t="n">
-        <v>-1.07896254566824</v>
+        <v>-1.00777580535413</v>
       </c>
       <c r="C57" t="n">
-        <v>1.69339160895754</v>
+        <v>0.927605800760507</v>
       </c>
       <c r="D57" t="n">
-        <v>0.749697282330951</v>
+        <v>1.21274859757059</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.09353614720575</v>
+        <v>-0.666420165980729</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.62656224754444</v>
+        <v>-1.20991904825062</v>
       </c>
       <c r="G57" t="n">
-        <v>1.99097802617244</v>
+        <v>2.00299064056249</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-0.926404370650189</v>
+        <v>-1.16111444311574</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.943775438545903</v>
+        <v>-1.03930539019974</v>
       </c>
       <c r="C58" t="n">
-        <v>1.45255213554957</v>
+        <v>1.11998225944905</v>
       </c>
       <c r="D58" t="n">
-        <v>1.06143184624167</v>
+        <v>1.28303159260534</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.16040276779906</v>
+        <v>-0.988342854283015</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.58346921965449</v>
+        <v>-1.3302611233148</v>
       </c>
       <c r="G58" t="n">
-        <v>2.0264015757379</v>
+        <v>1.97272809917932</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-0.814848205946014</v>
+        <v>-1.0562612167786</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.950005588750884</v>
+        <v>-1.12625203700085</v>
       </c>
       <c r="C59" t="n">
-        <v>1.5070966771222</v>
+        <v>1.26181470772453</v>
       </c>
       <c r="D59" t="n">
-        <v>0.650961170078069</v>
+        <v>1.04205544800632</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.06647885495189</v>
+        <v>-1.03988413683012</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.56898630400035</v>
+        <v>-1.35687606891765</v>
       </c>
       <c r="G59" t="n">
-        <v>1.96949025652864</v>
+        <v>2.04869433419933</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-1.20252115876519</v>
+        <v>-0.966345680523124</v>
       </c>
       <c r="B60" t="n">
-        <v>-1.26289166937104</v>
+        <v>-0.961692463360606</v>
       </c>
       <c r="C60" t="n">
-        <v>1.85924489103334</v>
+        <v>0.855759718993288</v>
       </c>
       <c r="D60" t="n">
-        <v>1.50051921340912</v>
+        <v>0.827606873162666</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.10530056554639</v>
+        <v>-0.984967239100858</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.86870575721841</v>
+        <v>-1.4823498996179</v>
       </c>
       <c r="G60" t="n">
-        <v>1.94587574413489</v>
+        <v>1.97206919332308</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-1.22303697399903</v>
+        <v>-0.997298186027931</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.08207948554586</v>
+        <v>-0.956504963979826</v>
       </c>
       <c r="C61" t="n">
-        <v>1.67167537178807</v>
+        <v>0.861587916568286</v>
       </c>
       <c r="D61" t="n">
-        <v>1.69167855876845</v>
+        <v>0.653196749720963</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.00634255093962</v>
+        <v>-0.744391786718141</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.08393200005627</v>
+        <v>-1.34551772711019</v>
       </c>
       <c r="G61" t="n">
-        <v>2.00034285667651</v>
+        <v>2.00494406433795</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-1.21235158286475</v>
+        <v>-1.0227070900544</v>
       </c>
       <c r="B62" t="n">
-        <v>-1.12359777457051</v>
+        <v>-0.963202809864946</v>
       </c>
       <c r="C62" t="n">
-        <v>1.5213013323003</v>
+        <v>1.02411474024136</v>
       </c>
       <c r="D62" t="n">
-        <v>1.51546289978738</v>
+        <v>1.0419796398753</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.84619135798078</v>
+        <v>-1.09227728451884</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.28354644180024</v>
+        <v>-1.47887773903069</v>
       </c>
       <c r="G62" t="n">
-        <v>2.04672259852648</v>
+        <v>1.98704404463085</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-0.958001603853333</v>
+        <v>-1.39700513024379</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.8993692027076</v>
+        <v>-0.88364284142552</v>
       </c>
       <c r="C63" t="n">
-        <v>1.37822491867672</v>
+        <v>0.977893645999992</v>
       </c>
       <c r="D63" t="n">
-        <v>1.05928522406236</v>
+        <v>1.419392471572</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.29470083767908</v>
+        <v>-0.508557492268645</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.64651272327031</v>
+        <v>-0.924390972435878</v>
       </c>
       <c r="G63" t="n">
-        <v>1.89047799321617</v>
+        <v>1.94656069778731</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-1.27536276641182</v>
+        <v>-0.968604318224198</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.976990408307566</v>
+        <v>-0.94486745395905</v>
       </c>
       <c r="C64" t="n">
-        <v>1.49016200090195</v>
+        <v>0.982921350826473</v>
       </c>
       <c r="D64" t="n">
-        <v>1.41971056965951</v>
+        <v>0.75817090325149</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.736866749144062</v>
+        <v>-1.03164193396789</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.84277345937123</v>
+        <v>-1.39329996799187</v>
       </c>
       <c r="G64" t="n">
-        <v>2.02105464849883</v>
+        <v>2.06494098619698</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-0.847656305929411</v>
+        <v>-1.0075693853944</v>
       </c>
       <c r="B65" t="n">
-        <v>-1.03491986929148</v>
+        <v>-0.947474996572187</v>
       </c>
       <c r="C65" t="n">
-        <v>1.49290154980687</v>
+        <v>1.14104273075859</v>
       </c>
       <c r="D65" t="n">
-        <v>0.835484319214822</v>
+        <v>0.989885859189356</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.32257434476121</v>
+        <v>-1.10472174636412</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.57179557822916</v>
+        <v>-1.44794207327263</v>
       </c>
       <c r="G65" t="n">
-        <v>1.89923295568174</v>
+        <v>1.99118093363954</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-0.966859894544063</v>
+        <v>-0.926953390851425</v>
       </c>
       <c r="B66" t="n">
-        <v>-1.14438254223359</v>
+        <v>-1.08929132905328</v>
       </c>
       <c r="C66" t="n">
-        <v>1.72764583222447</v>
+        <v>1.20342093761473</v>
       </c>
       <c r="D66" t="n">
-        <v>1.06632173138029</v>
+        <v>0.804169602752635</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.93805148303926</v>
+        <v>-1.52242126999129</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.44473122864685</v>
+        <v>-1.59095122303387</v>
       </c>
       <c r="G66" t="n">
-        <v>1.91330714548173</v>
+        <v>1.92043106497094</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-1.08690989713159</v>
+        <v>-0.969352404774595</v>
       </c>
       <c r="B67" t="n">
-        <v>-1.02994776522625</v>
+        <v>-0.99724655128973</v>
       </c>
       <c r="C67" t="n">
-        <v>1.62531007609202</v>
+        <v>1.09917480491043</v>
       </c>
       <c r="D67" t="n">
-        <v>1.26356430359305</v>
+        <v>1.05083418498411</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.13599121549723</v>
+        <v>-1.20176776683885</v>
       </c>
       <c r="F67" t="n">
-        <v>-2.28045511704982</v>
+        <v>-1.53272063801979</v>
       </c>
       <c r="G67" t="n">
-        <v>1.94615436066498</v>
+        <v>1.96167567765694</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-0.994272281164464</v>
+        <v>-1.0950642811588</v>
       </c>
       <c r="B68" t="n">
-        <v>-1.1001883626555</v>
+        <v>-1.16749834120273</v>
       </c>
       <c r="C68" t="n">
-        <v>1.85060463852639</v>
+        <v>1.22205056539699</v>
       </c>
       <c r="D68" t="n">
-        <v>1.18093938206877</v>
+        <v>1.11057534346574</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.12708748474776</v>
+        <v>-1.2558265031815</v>
       </c>
       <c r="F68" t="n">
-        <v>-2.35113830473558</v>
+        <v>-2.24369341870886</v>
       </c>
       <c r="G68" t="n">
-        <v>2.01540418122634</v>
+        <v>1.97892038480863</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-1.1056155334649</v>
+        <v>-1.0581699426278</v>
       </c>
       <c r="B69" t="n">
-        <v>-1.02399995515798</v>
+        <v>-0.846032886041014</v>
       </c>
       <c r="C69" t="n">
-        <v>1.7396912774281</v>
+        <v>0.960011289575424</v>
       </c>
       <c r="D69" t="n">
-        <v>1.14229098423029</v>
+        <v>0.986960695632756</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.695014349295919</v>
+        <v>-0.988367438773238</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.22429095041096</v>
+        <v>-2.07140561130063</v>
       </c>
       <c r="G69" t="n">
-        <v>2.03827940263371</v>
+        <v>2.1200323731154</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-1.08009249809604</v>
+        <v>-1.30614917032642</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.953313911626693</v>
+        <v>-1.01332223974296</v>
       </c>
       <c r="C70" t="n">
-        <v>1.39564378228288</v>
+        <v>1.01407062635783</v>
       </c>
       <c r="D70" t="n">
-        <v>1.09154544269743</v>
+        <v>1.45700975263033</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.834534396187224</v>
+        <v>-0.863047349237474</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.30304654107407</v>
+        <v>-1.95988591231835</v>
       </c>
       <c r="G70" t="n">
-        <v>2.13285068971632</v>
+        <v>2.10448432640695</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-1.10318965081216</v>
+        <v>-1.15868024016815</v>
       </c>
       <c r="B71" t="n">
-        <v>-1.19608934609335</v>
+        <v>-0.929926672164207</v>
       </c>
       <c r="C71" t="n">
-        <v>1.84648096471597</v>
+        <v>0.903058962992388</v>
       </c>
       <c r="D71" t="n">
-        <v>1.28921965851893</v>
+        <v>1.15081148323795</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.17454483679551</v>
+        <v>-0.769642143935971</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.91350687808134</v>
+        <v>-1.23016817994181</v>
       </c>
       <c r="G71" t="n">
-        <v>1.99770861772818</v>
+        <v>2.02643120529906</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-1.15580238914968</v>
+        <v>-0.860810049373569</v>
       </c>
       <c r="B72" t="n">
-        <v>-1.16782473520986</v>
+        <v>-1.02342712507535</v>
       </c>
       <c r="C72" t="n">
-        <v>1.70332786622827</v>
+        <v>1.08251362516263</v>
       </c>
       <c r="D72" t="n">
-        <v>1.45328383041402</v>
+        <v>0.827851258420954</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.15583817807755</v>
+        <v>-1.06428725985949</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.47946564691813</v>
+        <v>-1.69842174804039</v>
       </c>
       <c r="G72" t="n">
-        <v>1.96953393159989</v>
+        <v>1.86724155014206</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-1.17849255724955</v>
+        <v>-1.16866814803598</v>
       </c>
       <c r="B73" t="n">
-        <v>-1.09756473399481</v>
+        <v>-1.06466605340196</v>
       </c>
       <c r="C73" t="n">
-        <v>1.77693967215374</v>
+        <v>1.12123580714151</v>
       </c>
       <c r="D73" t="n">
-        <v>1.6660030342135</v>
+        <v>1.19369083123073</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.807341501960042</v>
+        <v>-1.14092763865667</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.33760851721762</v>
+        <v>-1.27806053262816</v>
       </c>
       <c r="G73" t="n">
-        <v>2.01039725443127</v>
+        <v>1.98286901246936</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-1.28415829375189</v>
+        <v>-0.961560198664224</v>
       </c>
       <c r="B74" t="n">
-        <v>-1.20548235809239</v>
+        <v>-1.25201347409089</v>
       </c>
       <c r="C74" t="n">
-        <v>1.74192331711395</v>
+        <v>1.39305569993577</v>
       </c>
       <c r="D74" t="n">
-        <v>1.59315813391328</v>
+        <v>0.719028191024087</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.375673227156798</v>
+        <v>-1.22766234202457</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.10585974179619</v>
+        <v>-2.23723458082572</v>
       </c>
       <c r="G74" t="n">
-        <v>2.01722811697472</v>
+        <v>1.9560641765316</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-0.977742463325561</v>
+        <v>-1.06334719856867</v>
       </c>
       <c r="B75" t="n">
-        <v>-1.01967875575339</v>
+        <v>-1.02753048131722</v>
       </c>
       <c r="C75" t="n">
-        <v>1.662703475576</v>
+        <v>1.00292126526262</v>
       </c>
       <c r="D75" t="n">
-        <v>1.10897485997792</v>
+        <v>0.941728667598156</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.26794190585329</v>
+        <v>-0.892344318837136</v>
       </c>
       <c r="F75" t="n">
-        <v>-2.19817877985664</v>
+        <v>-1.22506532180485</v>
       </c>
       <c r="G75" t="n">
-        <v>1.96420479538953</v>
+        <v>1.98885598511996</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-1.1966500420189</v>
+        <v>-1.17296043988271</v>
       </c>
       <c r="B76" t="n">
-        <v>-1.02411154230452</v>
+        <v>-0.886778394941041</v>
       </c>
       <c r="C76" t="n">
-        <v>1.76327217805841</v>
+        <v>0.846073210136428</v>
       </c>
       <c r="D76" t="n">
-        <v>1.76233550088254</v>
+        <v>1.21213992533508</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.759103694764635</v>
+        <v>-0.819507637872842</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.27682494761038</v>
+        <v>-1.23015635869382</v>
       </c>
       <c r="G76" t="n">
-        <v>2.11871152003093</v>
+        <v>2.00349455543974</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-0.959746182205807</v>
+        <v>-1.09204621911577</v>
       </c>
       <c r="B77" t="n">
-        <v>-1.02696943278567</v>
+        <v>-0.927497205722187</v>
       </c>
       <c r="C77" t="n">
-        <v>1.53656227943575</v>
+        <v>0.826417998524988</v>
       </c>
       <c r="D77" t="n">
-        <v>0.993141211534636</v>
+        <v>0.879587798078193</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.17929419290333</v>
+        <v>-0.658007024650343</v>
       </c>
       <c r="F77" t="n">
-        <v>-2.23269937459678</v>
+        <v>-1.23941569067636</v>
       </c>
       <c r="G77" t="n">
-        <v>2.05991091418986</v>
+        <v>1.93745659452584</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-1.20133868137818</v>
+        <v>-0.715837831345874</v>
       </c>
       <c r="B78" t="n">
-        <v>-1.18131854542129</v>
+        <v>-1.07262527332351</v>
       </c>
       <c r="C78" t="n">
-        <v>1.78055684742179</v>
+        <v>1.20377580567455</v>
       </c>
       <c r="D78" t="n">
-        <v>1.50280500085663</v>
+        <v>0.12663786028584</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.08504065701854</v>
+        <v>-1.50719058554236</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.7870298451569</v>
+        <v>-2.45020148623954</v>
       </c>
       <c r="G78" t="n">
-        <v>1.93953075404063</v>
+        <v>2.1557063442221</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-0.982798267947231</v>
+        <v>-0.82586678560958</v>
       </c>
       <c r="B79" t="n">
-        <v>-1.07389944850469</v>
+        <v>-1.04131476453463</v>
       </c>
       <c r="C79" t="n">
-        <v>1.68379579095841</v>
+        <v>1.23821944975776</v>
       </c>
       <c r="D79" t="n">
-        <v>0.849226289270428</v>
+        <v>0.687510197776711</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.01697121943835</v>
+        <v>-1.12820316433218</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.95621226015482</v>
+        <v>-1.68666576742755</v>
       </c>
       <c r="G79" t="n">
-        <v>2.02881425818728</v>
+        <v>1.96347316700936</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-1.24666040326543</v>
+        <v>-0.857711547891023</v>
       </c>
       <c r="B80" t="n">
-        <v>-0.875136054954384</v>
+        <v>-0.916307663891352</v>
       </c>
       <c r="C80" t="n">
-        <v>1.30945706410441</v>
+        <v>1.02728795057954</v>
       </c>
       <c r="D80" t="n">
-        <v>1.59164352872807</v>
+        <v>0.789817710881948</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.798242998025896</v>
+        <v>-1.16198789451702</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.20595235178426</v>
+        <v>-1.60641259864824</v>
       </c>
       <c r="G80" t="n">
-        <v>1.9841390500802</v>
+        <v>2.19746875933826</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-1.20481775634294</v>
+        <v>-1.18869893805426</v>
       </c>
       <c r="B81" t="n">
-        <v>-1.02396984610387</v>
+        <v>-0.942381999977194</v>
       </c>
       <c r="C81" t="n">
-        <v>1.4584802664486</v>
+        <v>1.00679891410611</v>
       </c>
       <c r="D81" t="n">
-        <v>1.44512263333788</v>
+        <v>1.29194795552744</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.672839846729276</v>
+        <v>-0.738027123768133</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.16262890091888</v>
+        <v>-1.27968427422974</v>
       </c>
       <c r="G81" t="n">
-        <v>1.98604243081891</v>
+        <v>1.93583349714667</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-1.14581647264375</v>
+        <v>-1.12646383117724</v>
       </c>
       <c r="B82" t="n">
-        <v>-1.11916778133774</v>
+        <v>-1.01757971681478</v>
       </c>
       <c r="C82" t="n">
-        <v>1.64290709812949</v>
+        <v>1.14975182416021</v>
       </c>
       <c r="D82" t="n">
-        <v>1.44158977943329</v>
+        <v>1.087532991193</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.808819088251344</v>
+        <v>-0.502071860473962</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.28322576949746</v>
+        <v>-1.16667492703387</v>
       </c>
       <c r="G82" t="n">
-        <v>2.0245738527646</v>
+        <v>2.11830980573544</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-1.27085463627274</v>
+        <v>-0.845592507772762</v>
       </c>
       <c r="B83" t="n">
-        <v>-0.970991908496596</v>
+        <v>-1.17407795278238</v>
       </c>
       <c r="C83" t="n">
-        <v>1.52541333080711</v>
+        <v>1.16647130901595</v>
       </c>
       <c r="D83" t="n">
-        <v>1.50611572535845</v>
+        <v>0.48152112126729</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.522392037013631</v>
+        <v>-1.21069994133207</v>
       </c>
       <c r="F83" t="n">
-        <v>-1.12005849112496</v>
+        <v>-2.31653790430072</v>
       </c>
       <c r="G83" t="n">
-        <v>1.91019565556755</v>
+        <v>1.87209736660405</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-1.0472992280605</v>
+        <v>-0.859853286953306</v>
       </c>
       <c r="B84" t="n">
-        <v>-0.966290644210728</v>
+        <v>-1.23097220237122</v>
       </c>
       <c r="C84" t="n">
-        <v>1.54268295799711</v>
+        <v>1.18967268212919</v>
       </c>
       <c r="D84" t="n">
-        <v>1.16130978330515</v>
+        <v>0.677177897769628</v>
       </c>
       <c r="E84" t="n">
-        <v>-1.12605596654652</v>
+        <v>-1.41286650897357</v>
       </c>
       <c r="F84" t="n">
-        <v>-2.16992107145705</v>
+        <v>-2.40036809841167</v>
       </c>
       <c r="G84" t="n">
-        <v>1.9992467897873</v>
+        <v>1.88001849448206</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-1.20181255649703</v>
+        <v>-1.21945277643959</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.898426678016927</v>
+        <v>-0.875782542909258</v>
       </c>
       <c r="C85" t="n">
-        <v>1.53423860109326</v>
+        <v>0.915123812941886</v>
       </c>
       <c r="D85" t="n">
-        <v>1.50590981331586</v>
+        <v>1.2203683397903</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.669058970004509</v>
+        <v>-0.636971690545032</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.4035823265241</v>
+        <v>-1.0960334215381</v>
       </c>
       <c r="G85" t="n">
-        <v>1.96801731635337</v>
+        <v>1.96468896158862</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-0.887330085068149</v>
+        <v>-0.913497621163849</v>
       </c>
       <c r="B86" t="n">
-        <v>-0.992044505449848</v>
+        <v>-0.999379432448466</v>
       </c>
       <c r="C86" t="n">
-        <v>1.57551053270838</v>
+        <v>1.10668926006982</v>
       </c>
       <c r="D86" t="n">
-        <v>0.839457883978786</v>
+        <v>0.92866542382443</v>
       </c>
       <c r="E86" t="n">
-        <v>-1.10921825626039</v>
+        <v>-1.37506739250414</v>
       </c>
       <c r="F86" t="n">
-        <v>-1.53972392645658</v>
+        <v>-2.36425351212264</v>
       </c>
       <c r="G86" t="n">
-        <v>1.98182214555367</v>
+        <v>1.99681674280382</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-0.945584161940929</v>
+        <v>-0.905739816283165</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.870903993279865</v>
+        <v>-1.07975038738253</v>
       </c>
       <c r="C87" t="n">
-        <v>1.34149850080478</v>
+        <v>1.12679271121872</v>
       </c>
       <c r="D87" t="n">
-        <v>0.924233806395678</v>
+        <v>0.727436229297699</v>
       </c>
       <c r="E87" t="n">
-        <v>-1.17968242863639</v>
+        <v>-1.19021752698688</v>
       </c>
       <c r="F87" t="n">
-        <v>-2.37713668627679</v>
+        <v>-2.27297000682435</v>
       </c>
       <c r="G87" t="n">
-        <v>2.01509696138887</v>
+        <v>2.04997265916035</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-1.18296816907809</v>
+        <v>-1.32071314368136</v>
       </c>
       <c r="B88" t="n">
-        <v>-1.25761341117579</v>
+        <v>-0.947720072490004</v>
       </c>
       <c r="C88" t="n">
-        <v>1.98777625218887</v>
+        <v>0.967929784921889</v>
       </c>
       <c r="D88" t="n">
-        <v>1.57306085712966</v>
+        <v>1.52566952170682</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.09590037883578</v>
+        <v>-0.672398097441198</v>
       </c>
       <c r="F88" t="n">
-        <v>-2.23871182164202</v>
+        <v>-1.15725303436788</v>
       </c>
       <c r="G88" t="n">
-        <v>1.98611527072206</v>
+        <v>1.96350571535759</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-1.06175962136217</v>
+        <v>-0.970455743177487</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.830230464403439</v>
+        <v>-0.863272329084352</v>
       </c>
       <c r="C89" t="n">
-        <v>1.2417129603905</v>
+        <v>1.03925764759795</v>
       </c>
       <c r="D89" t="n">
-        <v>1.29309278477551</v>
+        <v>0.895904132063284</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.720486853994428</v>
+        <v>-1.1689011058427</v>
       </c>
       <c r="F89" t="n">
-        <v>-1.34849306389228</v>
+        <v>-1.59777106514291</v>
       </c>
       <c r="G89" t="n">
-        <v>1.99783140179141</v>
+        <v>1.93300230959961</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-1.392487307978</v>
+        <v>-0.759231334572083</v>
       </c>
       <c r="B90" t="n">
-        <v>-1.14247190866372</v>
+        <v>-1.04613481336652</v>
       </c>
       <c r="C90" t="n">
-        <v>1.65976089898302</v>
+        <v>0.962024368059117</v>
       </c>
       <c r="D90" t="n">
-        <v>1.98251026591763</v>
+        <v>0.476572273693278</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.690617696741199</v>
+        <v>-1.34508235154227</v>
       </c>
       <c r="F90" t="n">
-        <v>-1.25665023481485</v>
+        <v>-1.71074229148361</v>
       </c>
       <c r="G90" t="n">
-        <v>1.90192414359302</v>
+        <v>2.06661592881448</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-1.25848983819206</v>
+        <v>-0.885859548377222</v>
       </c>
       <c r="B91" t="n">
-        <v>-1.03854474413955</v>
+        <v>-0.811217825338563</v>
       </c>
       <c r="C91" t="n">
-        <v>1.58277625099412</v>
+        <v>0.959701131687587</v>
       </c>
       <c r="D91" t="n">
-        <v>1.55500290193531</v>
+        <v>0.977297247686159</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.603451522706016</v>
+        <v>-1.39700610083059</v>
       </c>
       <c r="F91" t="n">
-        <v>-1.22346106597597</v>
+        <v>-1.67727090694121</v>
       </c>
       <c r="G91" t="n">
-        <v>2.01671480250975</v>
+        <v>2.08672772382888</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-1.28214186591713</v>
+        <v>-0.99310871597012</v>
       </c>
       <c r="B92" t="n">
-        <v>-1.11848475839413</v>
+        <v>-0.89448226518614</v>
       </c>
       <c r="C92" t="n">
-        <v>1.56340728531216</v>
+        <v>0.971303232469869</v>
       </c>
       <c r="D92" t="n">
-        <v>1.59760609642986</v>
+        <v>1.05957449167999</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.939831552246407</v>
+        <v>-1.2355593698902</v>
       </c>
       <c r="F92" t="n">
-        <v>-1.93518809009844</v>
+        <v>-1.51979983966332</v>
       </c>
       <c r="G92" t="n">
-        <v>1.95591453239272</v>
+        <v>2.00902703003617</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-1.0104146690236</v>
+        <v>-1.0336108027528</v>
       </c>
       <c r="B93" t="n">
-        <v>-1.16109892009959</v>
+        <v>-1.04648479895362</v>
       </c>
       <c r="C93" t="n">
-        <v>1.67587556996778</v>
+        <v>1.0835607634515</v>
       </c>
       <c r="D93" t="n">
-        <v>1.21923001753435</v>
+        <v>1.12011439468875</v>
       </c>
       <c r="E93" t="n">
-        <v>-1.20310934555094</v>
+        <v>-1.11992952737581</v>
       </c>
       <c r="F93" t="n">
-        <v>-2.38914577339088</v>
+        <v>-1.61003462088243</v>
       </c>
       <c r="G93" t="n">
-        <v>1.91553806167602</v>
+        <v>1.84877153149829</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-0.99993355373842</v>
+        <v>-1.21686912859971</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.937581900985966</v>
+        <v>-1.06383027172771</v>
       </c>
       <c r="C94" t="n">
-        <v>1.45828981000526</v>
+        <v>1.18817311605304</v>
       </c>
       <c r="D94" t="n">
-        <v>0.877885648676076</v>
+        <v>1.17436020862882</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.716838543874184</v>
+        <v>-0.69151108120974</v>
       </c>
       <c r="F94" t="n">
-        <v>-1.29403503114612</v>
+        <v>-1.11178514272757</v>
       </c>
       <c r="G94" t="n">
-        <v>1.97439757729655</v>
+        <v>1.95374512887981</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-1.0413532804971</v>
+        <v>-1.18634711721278</v>
       </c>
       <c r="B95" t="n">
-        <v>-1.50839035867045</v>
+        <v>-0.82516702715347</v>
       </c>
       <c r="C95" t="n">
-        <v>2.08476308261735</v>
+        <v>0.85250008767793</v>
       </c>
       <c r="D95" t="n">
-        <v>1.20907399406354</v>
+        <v>1.174275514065</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.23993478134589</v>
+        <v>-0.822132291082338</v>
       </c>
       <c r="F95" t="n">
-        <v>-2.21080853185161</v>
+        <v>-1.13352281823514</v>
       </c>
       <c r="G95" t="n">
-        <v>1.89894975298488</v>
+        <v>2.02095429531964</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-1.38274978480279</v>
+        <v>-1.02659813957328</v>
       </c>
       <c r="B96" t="n">
-        <v>-1.49062153961505</v>
+        <v>-0.951074619214464</v>
       </c>
       <c r="C96" t="n">
-        <v>2.13264839280927</v>
+        <v>1.09890917909334</v>
       </c>
       <c r="D96" t="n">
-        <v>1.86250359016534</v>
+        <v>0.977060506854751</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.858580323136889</v>
+        <v>-1.18383174086829</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.67491545461172</v>
+        <v>-2.36292810599368</v>
       </c>
       <c r="G96" t="n">
-        <v>1.98058974918806</v>
+        <v>2.02169423239722</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-1.1116457675675</v>
+        <v>-0.853800205218559</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.913326661021907</v>
+        <v>-0.973801283425179</v>
       </c>
       <c r="C97" t="n">
-        <v>1.46966611611274</v>
+        <v>0.86201822055011</v>
       </c>
       <c r="D97" t="n">
-        <v>1.21427325046614</v>
+        <v>0.74700055447434</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.11201744582108</v>
+        <v>-1.49781072841387</v>
       </c>
       <c r="F97" t="n">
-        <v>-2.12554586252929</v>
+        <v>-2.67061555513951</v>
       </c>
       <c r="G97" t="n">
-        <v>1.97016774949561</v>
+        <v>1.97828284961129</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-1.02896354445399</v>
+        <v>-1.24794506442824</v>
       </c>
       <c r="B98" t="n">
-        <v>-1.18672231981652</v>
+        <v>-1.02724468250945</v>
       </c>
       <c r="C98" t="n">
-        <v>1.60063140218063</v>
+        <v>1.07521686529966</v>
       </c>
       <c r="D98" t="n">
-        <v>1.19674977189573</v>
+        <v>1.1133526244026</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.09265352023904</v>
+        <v>-0.786942631155505</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.51282085703499</v>
+        <v>-2.00022375901348</v>
       </c>
       <c r="G98" t="n">
-        <v>1.92491982815541</v>
+        <v>1.99153844302971</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-1.00922227539638</v>
+        <v>-1.03074179487161</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.900358905524709</v>
+        <v>-1.04495050328281</v>
       </c>
       <c r="C99" t="n">
-        <v>1.43288018921104</v>
+        <v>1.03521805482463</v>
       </c>
       <c r="D99" t="n">
-        <v>1.24713223219562</v>
+        <v>0.903625086227355</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.08940113256717</v>
+        <v>-1.00859232634192</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.49478482051891</v>
+        <v>-1.34637327512631</v>
       </c>
       <c r="G99" t="n">
-        <v>2.09196479409449</v>
+        <v>1.93465830161549</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.798096634650025</v>
+        <v>-0.85895428932667</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.97256913457966</v>
+        <v>-0.91180009066645</v>
       </c>
       <c r="C100" t="n">
-        <v>1.53986477023435</v>
+        <v>0.882541540045693</v>
       </c>
       <c r="D100" t="n">
-        <v>0.582904565624719</v>
+        <v>0.646983735472033</v>
       </c>
       <c r="E100" t="n">
-        <v>-1.22559989538897</v>
+        <v>-1.15928367464314</v>
       </c>
       <c r="F100" t="n">
-        <v>-1.55534005693915</v>
+        <v>-1.67377355874374</v>
       </c>
       <c r="G100" t="n">
-        <v>2.0871877871359</v>
+        <v>1.98320318121244</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-1.03616465855562</v>
+        <v>-0.966733551879521</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.952618353398534</v>
+        <v>-0.994026580361482</v>
       </c>
       <c r="C101" t="n">
-        <v>1.54292068501053</v>
+        <v>0.824257502573004</v>
       </c>
       <c r="D101" t="n">
-        <v>1.04629573768225</v>
+        <v>0.746630882416344</v>
       </c>
       <c r="E101" t="n">
-        <v>-1.11022849415314</v>
+        <v>-1.23789058557937</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.44761034591444</v>
+        <v>-2.25056270534748</v>
       </c>
       <c r="G101" t="n">
-        <v>1.98829495160862</v>
+        <v>1.9488803761418</v>
       </c>
     </row>
   </sheetData>
@@ -3149,826 +3152,826 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0863356277782971</v>
+        <v>11.5683890090444</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0492993337805703</v>
+        <v>0.338088194365861</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.99779870629316</v>
+        <v>7.5167689671042</v>
       </c>
       <c r="B3" t="n">
-        <v>0.15298800570638</v>
+        <v>0.328472587283266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.271126427851581</v>
+        <v>16.2733859645855</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0824274983204428</v>
+        <v>0.355458887032553</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.165428800691322</v>
+        <v>4.3522758418666</v>
       </c>
       <c r="B5" t="n">
-        <v>0.121050547296904</v>
+        <v>0.26815075183019</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1.8630752435041</v>
+        <v>13.0368624847638</v>
       </c>
       <c r="B6" t="n">
-        <v>0.216369708735635</v>
+        <v>0.341387067853531</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5.544067389734</v>
+        <v>0.226469761257307</v>
       </c>
       <c r="B7" t="n">
-        <v>0.278212932758377</v>
+        <v>0.0821219384368621</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.52919977412697</v>
+        <v>0.116042582317039</v>
       </c>
       <c r="B8" t="n">
-        <v>0.141544209821089</v>
+        <v>0.0560607694434417</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.37684237192376</v>
+        <v>0.486815325279365</v>
       </c>
       <c r="B9" t="n">
-        <v>0.181232408215521</v>
+        <v>0.0993187347248634</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.267967456534222</v>
+        <v>0.189885300758575</v>
       </c>
       <c r="B10" t="n">
-        <v>0.101287251680931</v>
+        <v>0.0750822433259793</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0458350874129671</v>
+        <v>0.66014819395456</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0318970684405746</v>
+        <v>0.121915929155066</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3.68334801007339</v>
+        <v>4.74297646832417</v>
       </c>
       <c r="B12" t="n">
-        <v>0.436574187699516</v>
+        <v>0.268863107848805</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.258997783801403</v>
+        <v>0.177631748710596</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0801916801122085</v>
+        <v>0.070551937430387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3.25616275588524</v>
+        <v>8.33283764182142</v>
       </c>
       <c r="B14" t="n">
-        <v>0.252642592516943</v>
+        <v>0.300712081780094</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.12854393374165</v>
+        <v>0.369718554106459</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0590561892797051</v>
+        <v>0.137945885837678</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2.3584900780121</v>
+        <v>15.4684262351187</v>
       </c>
       <c r="B16" t="n">
-        <v>0.228040470102628</v>
+        <v>0.331000462185936</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.4763557841575</v>
+        <v>56.3684456973344</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0983244751537171</v>
+        <v>0.43346676154751</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13.8511536015251</v>
+        <v>16.9012599647499</v>
       </c>
       <c r="B18" t="n">
-        <v>0.328482439334902</v>
+        <v>0.347665994733376</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.22735453143351</v>
+        <v>20.9885637128342</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0809071455365906</v>
+        <v>0.374662282461041</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5.38427714188347</v>
+        <v>0.551392056016983</v>
       </c>
       <c r="B20" t="n">
-        <v>0.296194907686979</v>
+        <v>0.0997467592013251</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5.43143750557158</v>
+        <v>0.453696029755401</v>
       </c>
       <c r="B21" t="n">
-        <v>0.272172218554784</v>
+        <v>0.115949313837315</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.469391576416511</v>
+        <v>46.8062456560665</v>
       </c>
       <c r="B22" t="n">
-        <v>0.101348414198966</v>
+        <v>0.413984430675047</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.911616810327487</v>
+        <v>4.68724958037267</v>
       </c>
       <c r="B23" t="n">
-        <v>0.271959649765193</v>
+        <v>0.271508297118448</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1.05104729545581</v>
+        <v>0.36549329939339</v>
       </c>
       <c r="B24" t="n">
-        <v>0.298449041483031</v>
+        <v>0.192866122247021</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1.72495425276607</v>
+        <v>1.04055557674535</v>
       </c>
       <c r="B25" t="n">
-        <v>0.209258123636322</v>
+        <v>0.152448021541286</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.06171762874386</v>
+        <v>0.0557780797080419</v>
       </c>
       <c r="B26" t="n">
-        <v>0.159130591340906</v>
+        <v>0.0393492126275829</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3.45229715732911</v>
+        <v>0.240001471801126</v>
       </c>
       <c r="B27" t="n">
-        <v>0.239957192100911</v>
+        <v>0.0812829792059361</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2.8487391516695</v>
+        <v>0.441558304220056</v>
       </c>
       <c r="B28" t="n">
-        <v>0.257396839106155</v>
+        <v>0.0854632994637785</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1.35441053846894</v>
+        <v>28.7712712463918</v>
       </c>
       <c r="B29" t="n">
-        <v>0.149003943225824</v>
+        <v>0.396980480252191</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2.44767049225287</v>
+        <v>0.0551178131253609</v>
       </c>
       <c r="B30" t="n">
-        <v>0.200595165476196</v>
+        <v>0.0424691429129066</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.519205844720268</v>
+        <v>2.21654795213605</v>
       </c>
       <c r="B31" t="n">
-        <v>0.287328642045867</v>
+        <v>0.261331281195764</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.16472352267</v>
+        <v>3.87308267595424</v>
       </c>
       <c r="B32" t="n">
-        <v>0.0563918385651099</v>
+        <v>0.228273508782303</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.313626437008838</v>
+        <v>5.50702627715681</v>
       </c>
       <c r="B33" t="n">
-        <v>0.184075001289774</v>
+        <v>0.250260188795</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.0981075684547939</v>
+        <v>51.9680265132482</v>
       </c>
       <c r="B34" t="n">
-        <v>0.0479837988136204</v>
+        <v>0.453649048133006</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.271182373904435</v>
+        <v>23.2122258292981</v>
       </c>
       <c r="B35" t="n">
-        <v>0.0888361160665354</v>
+        <v>0.401197865828414</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3.28401663973021</v>
+        <v>0.389127653212696</v>
       </c>
       <c r="B36" t="n">
-        <v>0.285932971599364</v>
+        <v>0.08771615908716</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3.79693465445204</v>
+        <v>0.895024618806387</v>
       </c>
       <c r="B37" t="n">
-        <v>0.288292963349268</v>
+        <v>0.231832428096437</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.680039746912979</v>
+        <v>5.8701218671214</v>
       </c>
       <c r="B38" t="n">
-        <v>0.108641942379011</v>
+        <v>0.262591275496126</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.125349351618072</v>
+        <v>0.669164767021128</v>
       </c>
       <c r="B39" t="n">
-        <v>0.0568147396127777</v>
+        <v>0.11822089238383</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.108424811295662</v>
+        <v>0.333538386653868</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0619213969093702</v>
+        <v>0.280948729192149</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1.68339905708836</v>
+        <v>0.241225354643794</v>
       </c>
       <c r="B41" t="n">
-        <v>0.196476998864714</v>
+        <v>0.0833433697959959</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1.89055142530196</v>
+        <v>0.105072832237641</v>
       </c>
       <c r="B42" t="n">
-        <v>0.270690615826683</v>
+        <v>0.0583607543744376</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>26.3835430067625</v>
+        <v>3.70848034019965</v>
       </c>
       <c r="B43" t="n">
-        <v>0.407700329974567</v>
+        <v>0.217238188689724</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>17.5896962065552</v>
+        <v>2.08741673212465</v>
       </c>
       <c r="B44" t="n">
-        <v>0.373764353376738</v>
+        <v>0.171312068163269</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2.59618171404617</v>
+        <v>6.19372390531644</v>
       </c>
       <c r="B45" t="n">
-        <v>0.189119336865895</v>
+        <v>0.29092312159834</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1.93145653705338</v>
+        <v>25.1060193536307</v>
       </c>
       <c r="B46" t="n">
-        <v>0.169722047787594</v>
+        <v>0.370107357029959</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3.55732232734912</v>
+        <v>2.34817406821957</v>
       </c>
       <c r="B47" t="n">
-        <v>0.219217624998636</v>
+        <v>0.198414684769857</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2.88330259359595</v>
+        <v>0.94396216118515</v>
       </c>
       <c r="B48" t="n">
-        <v>0.231680514831135</v>
+        <v>0.151275994138381</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.358531693399633</v>
+        <v>2.88991918869925</v>
       </c>
       <c r="B49" t="n">
-        <v>0.208090726467349</v>
+        <v>0.214626053473262</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1.91452715947756</v>
+        <v>0.606274741129918</v>
       </c>
       <c r="B50" t="n">
-        <v>0.181388827400606</v>
+        <v>0.118305355840432</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>5.57541257428355</v>
+        <v>0.21387338824935</v>
       </c>
       <c r="B51" t="n">
-        <v>0.222638104324486</v>
+        <v>0.0901475494334218</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>31.5735251994042</v>
+        <v>19.66153614249</v>
       </c>
       <c r="B52" t="n">
-        <v>0.379787404051269</v>
+        <v>0.338382378406269</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.300939377594856</v>
+        <v>38.9950119134241</v>
       </c>
       <c r="B53" t="n">
-        <v>0.254600976024446</v>
+        <v>0.406237340284688</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>5.3572902669374</v>
+        <v>0.398187229826525</v>
       </c>
       <c r="B54" t="n">
-        <v>0.253852683769837</v>
+        <v>0.203845921486862</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.29420274659181</v>
+        <v>0.236702324974832</v>
       </c>
       <c r="B55" t="n">
-        <v>0.318353682711835</v>
+        <v>0.248196389841198</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.92004103868577</v>
+        <v>0.620598402548806</v>
       </c>
       <c r="B56" t="n">
-        <v>0.204171754715474</v>
+        <v>0.220667087892452</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>11.6207223049512</v>
+        <v>0.077236380746431</v>
       </c>
       <c r="B57" t="n">
-        <v>0.332655803807414</v>
+        <v>0.0412279003390561</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>10.2730679119135</v>
+        <v>0.638661122847845</v>
       </c>
       <c r="B58" t="n">
-        <v>0.297631287620834</v>
+        <v>0.109328307702039</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>9.2017196403911</v>
+        <v>1.06493921003801</v>
       </c>
       <c r="B59" t="n">
-        <v>0.297924236012824</v>
+        <v>0.137467165888243</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.47606095523608</v>
+        <v>2.16758897518088</v>
       </c>
       <c r="B60" t="n">
-        <v>0.169891988455624</v>
+        <v>0.238521709819269</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.984574505609113</v>
+        <v>0.785090694030021</v>
       </c>
       <c r="B61" t="n">
-        <v>0.23727448631518</v>
+        <v>0.126589174666853</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.167630880613551</v>
+        <v>4.36439052584692</v>
       </c>
       <c r="B62" t="n">
-        <v>0.0705686237677879</v>
+        <v>0.231122242218968</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>15.2214824649954</v>
+        <v>0.432517017865935</v>
       </c>
       <c r="B63" t="n">
-        <v>0.345166732768346</v>
+        <v>0.388601833058685</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.355568292250789</v>
+        <v>1.14022567898251</v>
       </c>
       <c r="B64" t="n">
-        <v>0.241587320377483</v>
+        <v>0.163945807509342</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>8.89177179491969</v>
+        <v>2.88315683923136</v>
       </c>
       <c r="B65" t="n">
-        <v>0.307061102554226</v>
+        <v>0.213364368039615</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2.35596713810603</v>
+        <v>5.13903623782153</v>
       </c>
       <c r="B66" t="n">
-        <v>0.203473585782476</v>
+        <v>0.322329586617625</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4.60646087749051</v>
+        <v>6.47568572579192</v>
       </c>
       <c r="B67" t="n">
-        <v>0.302188242536522</v>
+        <v>0.27519680524172</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>13.5251870863326</v>
+        <v>4.15598364426964</v>
       </c>
       <c r="B68" t="n">
-        <v>0.253431241110903</v>
+        <v>0.363394860191215</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.0565602176756068</v>
+        <v>0.886050324745984</v>
       </c>
       <c r="B69" t="n">
-        <v>0.0343274401650905</v>
+        <v>0.235089358466152</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.256141353113363</v>
+        <v>0.361914515780631</v>
       </c>
       <c r="B70" t="n">
-        <v>0.0853425299569945</v>
+        <v>0.219690553224404</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.55381452226335</v>
+        <v>0.0558992088844186</v>
       </c>
       <c r="B71" t="n">
-        <v>0.22158953259099</v>
+        <v>0.040876624646126</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2.84597647355129</v>
+        <v>28.3483693428384</v>
       </c>
       <c r="B72" t="n">
-        <v>0.221536500780651</v>
+        <v>0.387198124105135</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.537348608991749</v>
+        <v>0.168778039204899</v>
       </c>
       <c r="B73" t="n">
-        <v>0.117062337059761</v>
+        <v>0.074884361214175</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.172533681308587</v>
+        <v>3.11089720399603</v>
       </c>
       <c r="B74" t="n">
-        <v>0.145762564115357</v>
+        <v>0.366184743282852</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>8.48461860598068</v>
+        <v>0.0615941802778735</v>
       </c>
       <c r="B75" t="n">
-        <v>0.366153054723925</v>
+        <v>0.0430876738800586</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.30033705467351</v>
+        <v>0.0452931031064509</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0718836080877646</v>
+        <v>0.039715289593068</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>11.4782919716101</v>
+        <v>0.0723624693167379</v>
       </c>
       <c r="B77" t="n">
-        <v>0.377373288874311</v>
+        <v>0.0524703723060138</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.315036550007436</v>
+        <v>31.0882895419756</v>
       </c>
       <c r="B78" t="n">
-        <v>0.184078017526975</v>
+        <v>0.502885739773201</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1.00874976944891</v>
+        <v>26.7882993759712</v>
       </c>
       <c r="B79" t="n">
-        <v>0.209480296892954</v>
+        <v>0.381573571276267</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.146651681931078</v>
+        <v>13.2419829704158</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0606626619490599</v>
+        <v>0.322915939684369</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.211384764740758</v>
+        <v>0.174767536969033</v>
       </c>
       <c r="B81" t="n">
-        <v>0.0921416643377033</v>
+        <v>0.072246146506235</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.2643408949567</v>
+        <v>0.236346095867315</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0772397056815988</v>
+        <v>0.0964746862170469</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.290113978448889</v>
+        <v>14.9804871085493</v>
       </c>
       <c r="B83" t="n">
-        <v>0.136061738685914</v>
+        <v>0.345756826852147</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4.69301718237515</v>
+        <v>54.4598941919424</v>
       </c>
       <c r="B84" t="n">
-        <v>0.297330952158398</v>
+        <v>0.442573560204229</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1.18559540551918</v>
+        <v>0.299027501582134</v>
       </c>
       <c r="B85" t="n">
-        <v>0.153968927239872</v>
+        <v>0.171148730520213</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>7.02695160803683</v>
+        <v>26.8480103295061</v>
       </c>
       <c r="B86" t="n">
-        <v>0.285360274463945</v>
+        <v>0.453179911099886</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>8.86587296428568</v>
+        <v>16.6918334067364</v>
       </c>
       <c r="B87" t="n">
-        <v>0.411701258958386</v>
+        <v>0.327297776559418</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1.92693838648401</v>
+        <v>0.202557044077444</v>
       </c>
       <c r="B88" t="n">
-        <v>0.271414071542775</v>
+        <v>0.0994428744904686</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.922984223665536</v>
+        <v>8.550500374348</v>
       </c>
       <c r="B89" t="n">
-        <v>0.125861060754365</v>
+        <v>0.308799774668021</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.103120602337413</v>
+        <v>15.5792563569922</v>
       </c>
       <c r="B90" t="n">
-        <v>0.0577727350089045</v>
+        <v>0.398335257091274</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.0409123406542649</v>
+        <v>13.8856395093539</v>
       </c>
       <c r="B91" t="n">
-        <v>0.0351332936830652</v>
+        <v>0.371530829810284</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.319225418992821</v>
+        <v>5.94400156061536</v>
       </c>
       <c r="B92" t="n">
-        <v>0.233711096428964</v>
+        <v>0.280467451198003</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>25.0158707726839</v>
+        <v>11.4225087338425</v>
       </c>
       <c r="B93" t="n">
-        <v>0.392568333737844</v>
+        <v>0.317141031802915</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.36825670989805</v>
+        <v>0.268036346212446</v>
       </c>
       <c r="B94" t="n">
-        <v>0.0836293264821036</v>
+        <v>0.139810279799625</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>5.36668804690806</v>
+        <v>0.320956434967553</v>
       </c>
       <c r="B95" t="n">
-        <v>0.328812000137966</v>
+        <v>0.139356227687572</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.369324303579745</v>
+        <v>9.0710114956008</v>
       </c>
       <c r="B96" t="n">
-        <v>0.202574887265659</v>
+        <v>0.281126428818123</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2.94924882810346</v>
+        <v>221.278078600514</v>
       </c>
       <c r="B97" t="n">
-        <v>0.242657381719446</v>
+        <v>0.488282917497388</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4.05861659319195</v>
+        <v>0.297051776929365</v>
       </c>
       <c r="B98" t="n">
-        <v>0.250366019411133</v>
+        <v>0.248423777526836</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>3.00429840141309</v>
+        <v>0.702652418096569</v>
       </c>
       <c r="B99" t="n">
-        <v>0.245294579574002</v>
+        <v>0.128199200928095</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>8.06278341294175</v>
+        <v>20.177659502457</v>
       </c>
       <c r="B100" t="n">
-        <v>0.294274175506614</v>
+        <v>0.363885873606981</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2.39725500650093</v>
+        <v>3.27317200858374</v>
       </c>
       <c r="B101" t="n">
-        <v>0.206938821643952</v>
+        <v>0.373073656604797</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>3.62976250979344</v>
+        <v>10.1875301784995</v>
       </c>
       <c r="B104" t="n">
-        <v>0.205023884119459</v>
+        <v>0.23304594000802</v>
       </c>
     </row>
   </sheetData>
@@ -3984,18 +3987,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46016.9561628274</v>
+        <v>46026.2563933716</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
